--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="弦岸 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,36 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -749,7 +619,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1451,7 +1321,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1543,7 +1413,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1635,7 +1505,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1681,7 +1551,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1773,7 +1643,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1865,7 +1735,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1911,7 +1781,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2003,7 +1873,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2095,7 +1965,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2141,7 +2011,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2187,7 +2057,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2233,7 +2103,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2325,7 +2195,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2371,7 +2241,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2417,7 +2287,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2463,7 +2333,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2555,7 +2425,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2601,7 +2471,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2647,7 +2517,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2693,7 +2563,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2785,7 +2655,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2831,7 +2701,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2877,7 +2747,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2923,7 +2793,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2969,7 +2839,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3015,7 +2885,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3061,7 +2931,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3107,7 +2977,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3153,7 +3023,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3199,7 +3069,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3245,7 +3115,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3291,7 +3161,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3337,7 +3207,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3383,7 +3253,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3429,7 +3299,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3475,7 +3345,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3521,7 +3391,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3567,7 +3437,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3613,7 +3483,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3659,7 +3529,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3705,7 +3575,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3751,7 +3621,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3797,7 +3667,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3843,7 +3713,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3889,7 +3759,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3935,7 +3805,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3981,7 +3851,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4027,7 +3897,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4073,7 +3943,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4119,7 +3989,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4165,7 +4035,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4211,7 +4081,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4257,7 +4127,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4303,7 +4173,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4395,7 +4265,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4441,7 +4311,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4487,7 +4357,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4533,7 +4403,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4579,7 +4449,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4625,7 +4495,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4671,7 +4541,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4717,7 +4587,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4763,7 +4633,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4855,7 +4725,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4901,7 +4771,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4947,7 +4817,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4993,7 +4863,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5039,7 +4909,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5085,7 +4955,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5131,7 +5001,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5177,7 +5047,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5223,7 +5093,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5269,7 +5139,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5315,7 +5185,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5361,7 +5231,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5407,7 +5277,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-02</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5453,7 +5323,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5525,1120 +5395,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>弦岸 - 弦岸 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>105 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>12 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>10 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>78 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 293呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$734万
-$26,999/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,148万
-$36,218/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$1,049万
-$35,932/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$774万
-$37,776/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$972万
-$35,724/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$972万
-$35,467/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,139万
-$35,921/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$1,040万
-$35,634/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$757万
-$36,941/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$964万
-$35,426/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$964万
-$35,172/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,131万
-$35,669/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$773万
-$26,486/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$740万
-$36,122/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$715万
-$26,276/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$956万
-$34,898/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,123万
-$35,432/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$698万
-$23,901/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$732万
-$35,722/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$598万
-$21,982/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$598万
-$21,821/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,116万
-$35,205/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$658万
-$22,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$722万
-$35,215/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$590万
-$21,691/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$581万
-$21,193/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,099万
-$34,669/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$650万
-$22,264/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$484万
-$23,495/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$554万
-$20,364/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$563万
-$20,551/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,092万
-$34,454/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$614万
-$21,017/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$479万
-$23,252/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$567万
-$20,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$576万
-$21,018/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,086万
-$34,252/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$608万
-$20,808/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$434万
-$21,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$543万
-$19,963/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$552万
-$20,142/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$646万
-$20,446/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$632万
-$21,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$438万
-$21,238/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$538万
-$19,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$547万
-$19,974/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$639万
-$20,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$598万
-$20,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$425万
-$20,636/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$532万
-$19,562/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$542万
-$19,777/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$635万
-$20,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$592万
-$20,291/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$421万
-$20,427/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$529万
-$19,441/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$536万
-$19,577/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$644万
-$20,364/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$618万
-$21,182/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 206呎 (开放式)
-$403万
-$19,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$541万
-$19,893/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$533万
-$19,460/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$627万
-$19,845/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$584万
-$20,014/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$406万
-$19,815/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$547万
-$20,103/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$537万
-$19,591/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$634万
-$20,070/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$581万
-$19,911/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$396万
-$19,312/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$533万
-$19,599/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$525万
-$19,172/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,026万
-$32,372/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$576万
-$19,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$399万
-$19,454/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$539万
-$19,824/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$529万
-$19,314/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$626万
-$19,804/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$599万
-$20,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$387万
-$18,893/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$526万
-$19,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$516万
-$18,832/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 317呎 (1房)
-$1,022万
-$32,230/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$571万
-$19,568/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$394万
-$19,210/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$535万
-$19,654/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$525万
-$19,146/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$616万
-$19,484/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$592万
-$20,277/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$379万
-$18,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$517万
-$19,022/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$508万
-$18,522/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 316呎 (1房)
-$617万
-$19,519/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$561万
-$19,199/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$383万
-$18,673/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 272呎 (1房)
-$509万
-$18,721/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 274呎 (1房)
-$499万
-$18,223/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 279呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 292呎 (1房)
-$554万
-$18,979/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$369万
-$17,990/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 235呎 (1房)
-$630万
-$26,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 237呎 (1房)
-$530万
-$22,363/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="弦岸" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +147,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +222,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5395,4 +5573,1120 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>弦岸 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 293呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$734万
+$26,999/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1148万
+$36,218/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$1049万
+$35,932/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$774万
+$37,776/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$972万
+$35,724/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$972万
+$35,467/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1139万
+$35,921/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$1040万
+$35,634/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$757万
+$36,941/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$964万
+$35,426/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$964万
+$35,172/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1131万
+$35,669/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$773万
+$26,486/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$740万
+$36,122/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$715万
+$26,276/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$956万
+$34,898/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1123万
+$35,432/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$698万
+$23,901/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$732万
+$35,722/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$598万
+$21,982/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$598万
+$21,821/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1116万
+$35,205/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$658万
+$22,527/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$722万
+$35,215/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$590万
+$21,691/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$581万
+$21,193/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1099万
+$34,669/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$650万
+$22,264/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$484万
+$23,495/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$554万
+$20,364/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$563万
+$20,551/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1092万
+$34,454/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$614万
+$21,017/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$479万
+$23,252/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$567万
+$20,846/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$576万
+$21,018/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1086万
+$34,252/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$608万
+$20,808/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$434万
+$21,073/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$543万
+$19,963/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$552万
+$20,142/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$646万
+$20,446/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$632万
+$21,658/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$438万
+$21,238/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$538万
+$19,798/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$547万
+$19,974/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$639万
+$20,225/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$598万
+$20,490/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$425万
+$20,636/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$532万
+$19,562/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$542万
+$19,777/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$635万
+$20,108/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$592万
+$20,291/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$421万
+$20,427/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$529万
+$19,441/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$536万
+$19,577/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$644万
+$20,364/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$618万
+$21,182/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 206呎 (开放式)
+$403万
+$19,583/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$541万
+$19,893/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$533万
+$19,460/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$627万
+$19,845/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$584万
+$20,014/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$406万
+$19,815/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$547万
+$20,103/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$537万
+$19,591/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$634万
+$20,070/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$581万
+$19,911/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$396万
+$19,312/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$533万
+$19,599/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$525万
+$19,172/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1026万
+$32,372/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$576万
+$19,733/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$399万
+$19,454/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$539万
+$19,824/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$529万
+$19,314/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$626万
+$19,804/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$599万
+$20,527/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$387万
+$18,893/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$526万
+$19,338/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$516万
+$18,832/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 317呎 (1房)
+$1022万
+$32,230/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$571万
+$19,568/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$394万
+$19,210/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$535万
+$19,654/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$525万
+$19,146/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$616万
+$19,484/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$592万
+$20,277/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$379万
+$18,502/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$517万
+$19,022/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$508万
+$18,522/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 316呎 (1房)
+$617万
+$19,519/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$561万
+$19,199/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$383万
+$18,673/呎
+(24年-08月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 272呎 (1房)
+$509万
+$18,721/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 274呎 (1房)
+$499万
+$18,223/呎
+(25年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 279呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 292呎 (1房)
+$554万
+$18,979/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$369万
+$17,990/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 235呎 (1房)
+$630万
+$26,809/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 237呎 (1房)
+$530万
+$22,363/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -652,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:N107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -655,6 +655,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -712,6 +716,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -762,6 +786,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -808,6 +852,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7343700</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>26999</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -858,6 +918,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -908,6 +988,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -958,6 +1058,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1004,6 +1124,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>6438175</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>23497</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1050,6 +1186,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>6437512</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>23667</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1096,6 +1248,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5130400</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>25026</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1142,6 +1310,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>6950950</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>23805</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1188,6 +1372,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7606162</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>23994</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1234,6 +1434,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6384512</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>23301</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1280,6 +1496,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>6383850</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>23470</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1326,6 +1558,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>5017112</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>24474</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1372,6 +1620,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6893312</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>23607</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1418,6 +1682,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>7543888</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>23798</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1464,6 +1744,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6334825</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>23120</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1510,6 +1806,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7147000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>26276</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1556,6 +1868,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>4905812</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>23931</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1602,6 +1930,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>7734000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>26486</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1648,6 +1992,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>7490888</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>23631</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1694,6 +2054,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>5979000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>21821</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1740,6 +2116,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>5979000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>21982</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1786,6 +2178,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>4851488</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>23666</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1832,6 +2240,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>6979000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>23901</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1878,6 +2302,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>7441200</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>23474</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1924,6 +2364,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>5807000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>21193</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1970,6 +2426,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>21691</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2016,6 +2488,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>4782588</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>23330</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2062,6 +2550,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>6578000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>22527</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2108,6 +2612,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>7393500</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>23323</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2154,6 +2674,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>5631000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>20551</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2200,6 +2736,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>5539000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>20364</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2246,6 +2798,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>4840000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>23495</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2292,6 +2860,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>6501000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>22264</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2338,6 +2922,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>7280875</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>22968</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2384,6 +2984,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>5759000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>21018</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2430,6 +3046,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5670000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>20846</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2476,6 +3108,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>4790000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>23252</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2522,6 +3170,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>6137000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>21017</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2568,6 +3232,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>7235825</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>22826</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2614,6 +3294,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5519000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>20142</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2660,6 +3356,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>5430000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>19963</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2706,6 +3418,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>4341000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>21073</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2752,6 +3480,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>6076000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>20808</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2798,6 +3542,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7193425</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>22692</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2844,6 +3604,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>5473000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19974</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2890,6 +3666,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>5385000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>19798</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2936,6 +3728,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4375000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>21238</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2982,6 +3790,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6324000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>21658</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3028,6 +3852,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>6461000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>20446</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3074,6 +3914,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5419000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>19777</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3120,6 +3976,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>5321000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>19562</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3166,6 +4038,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>4251000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>20636</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3212,6 +4100,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>5983000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>20490</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3258,6 +4162,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6391000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>20225</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3304,6 +4224,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>5364000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>19577</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3350,6 +4286,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>5288000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>19441</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3396,6 +4348,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>4208000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>20427</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3442,6 +4410,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>5925000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>20291</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3488,6 +4472,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>6354000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>20108</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3534,6 +4534,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>5332000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>19460</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3580,6 +4596,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>5411000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>19893</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3626,6 +4658,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>4034000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>19583</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3672,6 +4720,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6185000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>21182</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3718,6 +4782,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>6435000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>20364</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3764,6 +4844,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>5368000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>19591</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3810,6 +4906,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5468000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>20103</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3856,6 +4968,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>4062000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>19815</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3902,6 +5030,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>5844000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>20014</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3948,6 +5092,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>6271000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>19845</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3994,6 +5154,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>5253000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>19172</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4040,6 +5216,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>5331000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>19599</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4086,6 +5278,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>3959000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>19312</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4132,6 +5340,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5814000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>19911</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4178,6 +5402,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>6342000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>20070</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4224,6 +5464,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>5292000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>19314</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4270,6 +5526,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5392000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>19824</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4316,6 +5588,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>19454</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4362,6 +5650,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>5762000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>19733</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4408,6 +5712,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>6798575</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>21447</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4454,6 +5774,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>5160000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>18832</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4500,6 +5836,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>5260000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>19338</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4546,6 +5898,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>3873000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>18893</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4592,6 +5960,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>5994000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>20527</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4638,6 +6022,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>6258000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>19804</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4684,6 +6084,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5246000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>19146</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4730,6 +6146,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>5346000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>19654</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4776,6 +6208,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>3938000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>19210</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4822,6 +6270,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>5714000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>19568</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4868,6 +6332,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>6768762</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>21353</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4914,6 +6394,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>5075000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>18522</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4960,6 +6456,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>5174000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>19022</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5006,6 +6518,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>3793000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>18502</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5052,6 +6580,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>5921000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>20277</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5098,6 +6642,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>6157000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>19484</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5144,6 +6704,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>4993000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>18223</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5190,6 +6766,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>5092000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>18721</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5236,6 +6828,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>3828000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>18673</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5282,6 +6890,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>5606000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>19199</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5328,6 +6952,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>6168000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>19519</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5374,6 +7014,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>22363</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5420,6 +7076,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>26809</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5466,6 +7138,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>3688000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>17990</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5512,6 +7200,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5542000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>18979</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5562,13 +7266,33 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5730,7 +7454,7 @@
           <t>D | 272呎 (1房)
 $734万
 $26,999/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -5855,7 +7579,7 @@
           <t>B | 292呎 (1房)
 $773万
 $26,486/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -5871,7 +7595,7 @@
           <t>D | 272呎 (1房)
 $715万
 $26,276/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -5902,7 +7626,7 @@
           <t>B | 292呎 (1房)
 $698万
 $23,901/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -5918,7 +7642,7 @@
           <t>D | 272呎 (1房)
 $598万
 $21,982/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -5926,7 +7650,7 @@
           <t>E | 274呎 (1房)
 $598万
 $21,821/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -5949,7 +7673,7 @@
           <t>B | 292呎 (1房)
 $658万
 $22,527/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -5965,7 +7689,7 @@
           <t>D | 272呎 (1房)
 $590万
 $21,691/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -5973,7 +7697,7 @@
           <t>E | 274呎 (1房)
 $581万
 $21,193/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -5996,7 +7720,7 @@
           <t>B | 292呎 (1房)
 $650万
 $22,264/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -6004,7 +7728,7 @@
           <t>C | 206呎 (开放式)
 $484万
 $23,495/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -6012,7 +7736,7 @@
           <t>D | 272呎 (1房)
 $554万
 $20,364/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -6020,7 +7744,7 @@
           <t>E | 274呎 (1房)
 $563万
 $20,551/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -6043,7 +7767,7 @@
           <t>B | 292呎 (1房)
 $614万
 $21,017/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -6051,7 +7775,7 @@
           <t>C | 206呎 (开放式)
 $479万
 $23,252/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -6059,7 +7783,7 @@
           <t>D | 272呎 (1房)
 $567万
 $20,846/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -6067,7 +7791,7 @@
           <t>E | 274呎 (1房)
 $576万
 $21,018/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -6090,7 +7814,7 @@
           <t>B | 292呎 (1房)
 $608万
 $20,808/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -6098,7 +7822,7 @@
           <t>C | 206呎 (开放式)
 $434万
 $21,073/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -6106,7 +7830,7 @@
           <t>D | 272呎 (1房)
 $543万
 $19,963/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -6114,7 +7838,7 @@
           <t>E | 274呎 (1房)
 $552万
 $20,142/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -6129,7 +7853,7 @@
           <t>A | 316呎 (1房)
 $646万
 $20,446/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -6137,7 +7861,7 @@
           <t>B | 292呎 (1房)
 $632万
 $21,658/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -6145,7 +7869,7 @@
           <t>C | 206呎 (开放式)
 $438万
 $21,238/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -6153,7 +7877,7 @@
           <t>D | 272呎 (1房)
 $538万
 $19,798/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -6161,7 +7885,7 @@
           <t>E | 274呎 (1房)
 $547万
 $19,974/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -6176,7 +7900,7 @@
           <t>A | 316呎 (1房)
 $639万
 $20,225/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -6184,7 +7908,7 @@
           <t>B | 292呎 (1房)
 $598万
 $20,490/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -6192,7 +7916,7 @@
           <t>C | 206呎 (开放式)
 $425万
 $20,636/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -6200,7 +7924,7 @@
           <t>D | 272呎 (1房)
 $532万
 $19,562/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -6208,7 +7932,7 @@
           <t>E | 274呎 (1房)
 $542万
 $19,777/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -6223,7 +7947,7 @@
           <t>A | 316呎 (1房)
 $635万
 $20,108/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -6231,7 +7955,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,291/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -6239,7 +7963,7 @@
           <t>C | 206呎 (开放式)
 $421万
 $20,427/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -6247,7 +7971,7 @@
           <t>D | 272呎 (1房)
 $529万
 $19,441/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -6255,7 +7979,7 @@
           <t>E | 274呎 (1房)
 $536万
 $19,577/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -6270,7 +7994,7 @@
           <t>A | 316呎 (1房)
 $644万
 $20,364/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -6278,7 +8002,7 @@
           <t>B | 292呎 (1房)
 $618万
 $21,182/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -6286,7 +8010,7 @@
           <t>C | 206呎 (开放式)
 $403万
 $19,583/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -6294,7 +8018,7 @@
           <t>D | 272呎 (1房)
 $541万
 $19,893/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -6302,7 +8026,7 @@
           <t>E | 274呎 (1房)
 $533万
 $19,460/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -6317,7 +8041,7 @@
           <t>A | 316呎 (1房)
 $627万
 $19,845/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -6325,7 +8049,7 @@
           <t>B | 292呎 (1房)
 $584万
 $20,014/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -6333,7 +8057,7 @@
           <t>C | 205呎 (开放式)
 $406万
 $19,815/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -6341,7 +8065,7 @@
           <t>D | 272呎 (1房)
 $547万
 $20,103/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -6349,7 +8073,7 @@
           <t>E | 274呎 (1房)
 $537万
 $19,591/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -6364,7 +8088,7 @@
           <t>A | 316呎 (1房)
 $634万
 $20,070/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -6372,7 +8096,7 @@
           <t>B | 292呎 (1房)
 $581万
 $19,911/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -6380,7 +8104,7 @@
           <t>C | 205呎 (开放式)
 $396万
 $19,312/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -6388,7 +8112,7 @@
           <t>D | 272呎 (1房)
 $533万
 $19,599/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -6396,7 +8120,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,172/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -6419,7 +8143,7 @@
           <t>B | 292呎 (1房)
 $576万
 $19,733/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -6427,7 +8151,7 @@
           <t>C | 205呎 (开放式)
 $399万
 $19,454/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -6435,7 +8159,7 @@
           <t>D | 272呎 (1房)
 $539万
 $19,824/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -6443,7 +8167,7 @@
           <t>E | 274呎 (1房)
 $529万
 $19,314/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -6458,7 +8182,7 @@
           <t>A | 316呎 (1房)
 $626万
 $19,804/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -6466,7 +8190,7 @@
           <t>B | 292呎 (1房)
 $599万
 $20,527/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -6474,7 +8198,7 @@
           <t>C | 205呎 (开放式)
 $387万
 $18,893/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -6482,7 +8206,7 @@
           <t>D | 272呎 (1房)
 $526万
 $19,338/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -6490,7 +8214,7 @@
           <t>E | 274呎 (1房)
 $516万
 $18,832/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -6513,7 +8237,7 @@
           <t>B | 292呎 (1房)
 $571万
 $19,568/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -6521,7 +8245,7 @@
           <t>C | 205呎 (开放式)
 $394万
 $19,210/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -6529,7 +8253,7 @@
           <t>D | 272呎 (1房)
 $535万
 $19,654/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -6537,7 +8261,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,146/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -6552,7 +8276,7 @@
           <t>A | 316呎 (1房)
 $616万
 $19,484/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -6560,7 +8284,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,277/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -6568,7 +8292,7 @@
           <t>C | 205呎 (开放式)
 $379万
 $18,502/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -6576,7 +8300,7 @@
           <t>D | 272呎 (1房)
 $517万
 $19,022/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -6584,7 +8308,7 @@
           <t>E | 274呎 (1房)
 $508万
 $18,522/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -6599,7 +8323,7 @@
           <t>A | 316呎 (1房)
 $617万
 $19,519/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -6607,7 +8331,7 @@
           <t>B | 292呎 (1房)
 $561万
 $19,199/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -6615,7 +8339,7 @@
           <t>C | 205呎 (开放式)
 $383万
 $18,673/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -6623,7 +8347,7 @@
           <t>D | 272呎 (1房)
 $509万
 $18,721/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -6631,7 +8355,7 @@
           <t>E | 274呎 (1房)
 $499万
 $18,223/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -6654,7 +8378,7 @@
           <t>B | 292呎 (1房)
 $554万
 $18,979/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -6662,7 +8386,7 @@
           <t>C | 205呎 (开放式)
 $369万
 $17,990/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -6670,7 +8394,7 @@
           <t>D | 235呎 (1房)
 $630万
 $26,809/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -6678,7 +8402,7 @@
           <t>E | 237呎 (1房)
 $530万
 $22,363/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>6438175</v>
+        <v>6449837</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>23497</v>
+        <v>23540</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6437512</v>
+        <v>6449173</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>23667</v>
+        <v>23710</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5130400</v>
+        <v>5139693</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>25026</v>
+        <v>25072</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>6950950</v>
+        <v>6963540</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>23805</v>
+        <v>23848</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>7606162</v>
+        <v>7619940</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>23994</v>
+        <v>24038</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>6384512</v>
+        <v>6396077</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>23301</v>
+        <v>23343</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>6383850</v>
+        <v>6395413</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>23470</v>
+        <v>23513</v>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>5017112</v>
+        <v>5026200</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>24474</v>
+        <v>24518</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6893312</v>
+        <v>6905798</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>23607</v>
+        <v>23650</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>7543888</v>
+        <v>7557552</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>23798</v>
+        <v>23841</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>6334825</v>
+        <v>6346299</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>23120</v>
+        <v>23162</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>4905812</v>
+        <v>4914698</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>23931</v>
+        <v>23974</v>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>7490888</v>
+        <v>7504456</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>23631</v>
+        <v>23673</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2178,14 +2178,14 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>4851488</v>
+        <v>5528865</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>23666</v>
+        <v>26970</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2306,10 +2306,10 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>7441200</v>
+        <v>7454678</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>23474</v>
+        <v>23516</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2488,14 +2488,14 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>4782588</v>
+        <v>5504488</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>23330</v>
+        <v>26851</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2616,10 +2616,10 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>7393500</v>
+        <v>7406892</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>23323</v>
+        <v>23366</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>7280875</v>
+        <v>7294063</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>22968</v>
+        <v>23010</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3232,14 +3232,14 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>7235825</v>
+        <v>7918450</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>22826</v>
+        <v>24979</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3542,14 +3542,14 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>7193425</v>
+        <v>7844905</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>22692</v>
+        <v>24747</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -5712,14 +5712,14 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="K82" s="5" t="n">
-        <v>6798575</v>
+        <v>7183400</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>21447</v>
+        <v>22661</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -6332,14 +6332,14 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>6768762</v>
+        <v>7075272</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>21353</v>
+        <v>22319</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K42" s="5" t="n">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -7454,7 +7454,7 @@
           <t>D | 272呎 (1房)
 $734万
 $26,999/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -7579,7 +7579,7 @@
           <t>B | 292呎 (1房)
 $773万
 $26,486/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -7595,7 +7595,7 @@
           <t>D | 272呎 (1房)
 $715万
 $26,276/呎
-(26年-06月-07日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -7626,7 +7626,7 @@
           <t>B | 292呎 (1房)
 $698万
 $23,901/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -7642,7 +7642,7 @@
           <t>D | 272呎 (1房)
 $598万
 $21,982/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -7650,7 +7650,7 @@
           <t>E | 274呎 (1房)
 $598万
 $21,821/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
           <t>B | 292呎 (1房)
 $658万
 $22,527/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -7689,7 +7689,7 @@
           <t>D | 272呎 (1房)
 $590万
 $21,691/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -7697,7 +7697,7 @@
           <t>E | 274呎 (1房)
 $581万
 $21,193/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
           <t>B | 292呎 (1房)
 $650万
 $22,264/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -7728,7 +7728,7 @@
           <t>C | 206呎 (开放式)
 $484万
 $23,495/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -7736,7 +7736,7 @@
           <t>D | 272呎 (1房)
 $554万
 $20,364/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -7744,7 +7744,7 @@
           <t>E | 274呎 (1房)
 $563万
 $20,551/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
           <t>B | 292呎 (1房)
 $614万
 $21,017/呎
-(26年-01月-25日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -7775,7 +7775,7 @@
           <t>C | 206呎 (开放式)
 $479万
 $23,252/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -7783,7 +7783,7 @@
           <t>D | 272呎 (1房)
 $567万
 $20,846/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -7791,7 +7791,7 @@
           <t>E | 274呎 (1房)
 $576万
 $21,018/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
           <t>B | 292呎 (1房)
 $608万
 $20,808/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -7822,7 +7822,7 @@
           <t>C | 206呎 (开放式)
 $434万
 $21,073/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -7830,7 +7830,7 @@
           <t>D | 272呎 (1房)
 $543万
 $19,963/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -7838,7 +7838,7 @@
           <t>E | 274呎 (1房)
 $552万
 $20,142/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
           <t>A | 316呎 (1房)
 $646万
 $20,446/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -7861,7 +7861,7 @@
           <t>B | 292呎 (1房)
 $632万
 $21,658/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -7869,7 +7869,7 @@
           <t>C | 206呎 (开放式)
 $438万
 $21,238/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -7877,7 +7877,7 @@
           <t>D | 272呎 (1房)
 $538万
 $19,798/呎
-(26年-01月-14日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -7885,7 +7885,7 @@
           <t>E | 274呎 (1房)
 $547万
 $19,974/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
           <t>A | 316呎 (1房)
 $639万
 $20,225/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -7908,7 +7908,7 @@
           <t>B | 292呎 (1房)
 $598万
 $20,490/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -7916,7 +7916,7 @@
           <t>C | 206呎 (开放式)
 $425万
 $20,636/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -7924,7 +7924,7 @@
           <t>D | 272呎 (1房)
 $532万
 $19,562/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -7932,7 +7932,7 @@
           <t>E | 274呎 (1房)
 $542万
 $19,777/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
           <t>A | 316呎 (1房)
 $635万
 $20,108/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -7955,7 +7955,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,291/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -7963,7 +7963,7 @@
           <t>C | 206呎 (开放式)
 $421万
 $20,427/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -7971,7 +7971,7 @@
           <t>D | 272呎 (1房)
 $529万
 $19,441/呎
-(25年-12月-23日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -7979,7 +7979,7 @@
           <t>E | 274呎 (1房)
 $536万
 $19,577/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
           <t>A | 316呎 (1房)
 $644万
 $20,364/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -8002,7 +8002,7 @@
           <t>B | 292呎 (1房)
 $618万
 $21,182/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -8010,7 +8010,7 @@
           <t>C | 206呎 (开放式)
 $403万
 $19,583/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -8018,7 +8018,7 @@
           <t>D | 272呎 (1房)
 $541万
 $19,893/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -8026,7 +8026,7 @@
           <t>E | 274呎 (1房)
 $533万
 $19,460/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
           <t>A | 316呎 (1房)
 $627万
 $19,845/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>B | 292呎 (1房)
 $584万
 $20,014/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -8057,7 +8057,7 @@
           <t>C | 205呎 (开放式)
 $406万
 $19,815/呎
-(24年-09月-16日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -8065,7 +8065,7 @@
           <t>D | 272呎 (1房)
 $547万
 $20,103/呎
-(25年-06月-09日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -8073,7 +8073,7 @@
           <t>E | 274呎 (1房)
 $537万
 $19,591/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
           <t>A | 316呎 (1房)
 $634万
 $20,070/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -8096,7 +8096,7 @@
           <t>B | 292呎 (1房)
 $581万
 $19,911/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -8104,7 +8104,7 @@
           <t>C | 205呎 (开放式)
 $396万
 $19,312/呎
-(24年-09月-04日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -8112,7 +8112,7 @@
           <t>D | 272呎 (1房)
 $533万
 $19,599/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -8120,7 +8120,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,172/呎
-(25年-08月-07日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
           <t>B | 292呎 (1房)
 $576万
 $19,733/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -8151,7 +8151,7 @@
           <t>C | 205呎 (开放式)
 $399万
 $19,454/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -8159,7 +8159,7 @@
           <t>D | 272呎 (1房)
 $539万
 $19,824/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -8167,7 +8167,7 @@
           <t>E | 274呎 (1房)
 $529万
 $19,314/呎
-(25年-08月-21日)</t>
+(25年-08月)</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
           <t>A | 316呎 (1房)
 $626万
 $19,804/呎
-(25年-07月-01日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -8190,7 +8190,7 @@
           <t>B | 292呎 (1房)
 $599万
 $20,527/呎
-(25年-08月-06日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -8198,7 +8198,7 @@
           <t>C | 205呎 (开放式)
 $387万
 $18,893/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -8206,7 +8206,7 @@
           <t>D | 272呎 (1房)
 $526万
 $19,338/呎
-(25年-04月-02日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -8214,7 +8214,7 @@
           <t>E | 274呎 (1房)
 $516万
 $18,832/呎
-(25年-07月-17日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
           <t>B | 292呎 (1房)
 $571万
 $19,568/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -8245,7 +8245,7 @@
           <t>C | 205呎 (开放式)
 $394万
 $19,210/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -8253,7 +8253,7 @@
           <t>D | 272呎 (1房)
 $535万
 $19,654/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -8261,7 +8261,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,146/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
           <t>A | 316呎 (1房)
 $616万
 $19,484/呎
-(25年-08月-03日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -8284,7 +8284,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,277/呎
-(25年-08月-13日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -8292,7 +8292,7 @@
           <t>C | 205呎 (开放式)
 $379万
 $18,502/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -8300,7 +8300,7 @@
           <t>D | 272呎 (1房)
 $517万
 $19,022/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -8308,7 +8308,7 @@
           <t>E | 274呎 (1房)
 $508万
 $18,522/呎
-(25年-07月-14日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
           <t>A | 316呎 (1房)
 $617万
 $19,519/呎
-(25年-08月-28日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -8331,7 +8331,7 @@
           <t>B | 292呎 (1房)
 $561万
 $19,199/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -8339,7 +8339,7 @@
           <t>C | 205呎 (开放式)
 $383万
 $18,673/呎
-(24年-08月-22日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -8347,7 +8347,7 @@
           <t>D | 272呎 (1房)
 $509万
 $18,721/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -8355,7 +8355,7 @@
           <t>E | 274呎 (1房)
 $499万
 $18,223/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
           <t>B | 292呎 (1房)
 $554万
 $18,979/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -8386,7 +8386,7 @@
           <t>C | 205呎 (开放式)
 $369万
 $17,990/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -8394,7 +8394,7 @@
           <t>D | 235呎 (1房)
 $630万
 $26,809/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -8402,7 +8402,7 @@
           <t>E | 237呎 (1房)
 $530万
 $22,363/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -7454,7 +7454,7 @@
           <t>D | 272呎 (1房)
 $734万
 $26,999/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -7579,7 +7579,7 @@
           <t>B | 292呎 (1房)
 $773万
 $26,486/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -7595,7 +7595,7 @@
           <t>D | 272呎 (1房)
 $715万
 $26,276/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -7626,7 +7626,7 @@
           <t>B | 292呎 (1房)
 $698万
 $23,901/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -7642,7 +7642,7 @@
           <t>D | 272呎 (1房)
 $598万
 $21,982/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -7650,7 +7650,7 @@
           <t>E | 274呎 (1房)
 $598万
 $21,821/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -7673,7 +7673,7 @@
           <t>B | 292呎 (1房)
 $658万
 $22,527/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -7689,7 +7689,7 @@
           <t>D | 272呎 (1房)
 $590万
 $21,691/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -7697,7 +7697,7 @@
           <t>E | 274呎 (1房)
 $581万
 $21,193/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
           <t>B | 292呎 (1房)
 $650万
 $22,264/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -7728,7 +7728,7 @@
           <t>C | 206呎 (开放式)
 $484万
 $23,495/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -7736,7 +7736,7 @@
           <t>D | 272呎 (1房)
 $554万
 $20,364/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -7744,7 +7744,7 @@
           <t>E | 274呎 (1房)
 $563万
 $20,551/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
     </row>
@@ -7767,7 +7767,7 @@
           <t>B | 292呎 (1房)
 $614万
 $21,017/呎
-(26年-01月)</t>
+(26年-01月-25日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -7775,7 +7775,7 @@
           <t>C | 206呎 (开放式)
 $479万
 $23,252/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -7783,7 +7783,7 @@
           <t>D | 272呎 (1房)
 $567万
 $20,846/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -7791,7 +7791,7 @@
           <t>E | 274呎 (1房)
 $576万
 $21,018/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
           <t>B | 292呎 (1房)
 $608万
 $20,808/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -7822,7 +7822,7 @@
           <t>C | 206呎 (开放式)
 $434万
 $21,073/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -7830,7 +7830,7 @@
           <t>D | 272呎 (1房)
 $543万
 $19,963/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -7838,7 +7838,7 @@
           <t>E | 274呎 (1房)
 $552万
 $20,142/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -7853,7 +7853,7 @@
           <t>A | 316呎 (1房)
 $646万
 $20,446/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -7861,7 +7861,7 @@
           <t>B | 292呎 (1房)
 $632万
 $21,658/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -7869,7 +7869,7 @@
           <t>C | 206呎 (开放式)
 $438万
 $21,238/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -7877,7 +7877,7 @@
           <t>D | 272呎 (1房)
 $538万
 $19,798/呎
-(26年-01月)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -7885,7 +7885,7 @@
           <t>E | 274呎 (1房)
 $547万
 $19,974/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
           <t>A | 316呎 (1房)
 $639万
 $20,225/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -7908,7 +7908,7 @@
           <t>B | 292呎 (1房)
 $598万
 $20,490/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -7916,7 +7916,7 @@
           <t>C | 206呎 (开放式)
 $425万
 $20,636/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -7924,7 +7924,7 @@
           <t>D | 272呎 (1房)
 $532万
 $19,562/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -7932,7 +7932,7 @@
           <t>E | 274呎 (1房)
 $542万
 $19,777/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
           <t>A | 316呎 (1房)
 $635万
 $20,108/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -7955,7 +7955,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,291/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -7963,7 +7963,7 @@
           <t>C | 206呎 (开放式)
 $421万
 $20,427/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -7971,7 +7971,7 @@
           <t>D | 272呎 (1房)
 $529万
 $19,441/呎
-(25年-12月)</t>
+(25年-12月-23日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -7979,7 +7979,7 @@
           <t>E | 274呎 (1房)
 $536万
 $19,577/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
           <t>A | 316呎 (1房)
 $644万
 $20,364/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -8002,7 +8002,7 @@
           <t>B | 292呎 (1房)
 $618万
 $21,182/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -8010,7 +8010,7 @@
           <t>C | 206呎 (开放式)
 $403万
 $19,583/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -8018,7 +8018,7 @@
           <t>D | 272呎 (1房)
 $541万
 $19,893/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -8026,7 +8026,7 @@
           <t>E | 274呎 (1房)
 $533万
 $19,460/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
           <t>A | 316呎 (1房)
 $627万
 $19,845/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -8049,7 +8049,7 @@
           <t>B | 292呎 (1房)
 $584万
 $20,014/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -8057,7 +8057,7 @@
           <t>C | 205呎 (开放式)
 $406万
 $19,815/呎
-(24年-09月)</t>
+(24年-09月-16日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -8065,7 +8065,7 @@
           <t>D | 272呎 (1房)
 $547万
 $20,103/呎
-(25年-06月)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -8073,7 +8073,7 @@
           <t>E | 274呎 (1房)
 $537万
 $19,591/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8088,7 @@
           <t>A | 316呎 (1房)
 $634万
 $20,070/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -8096,7 +8096,7 @@
           <t>B | 292呎 (1房)
 $581万
 $19,911/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -8104,7 +8104,7 @@
           <t>C | 205呎 (开放式)
 $396万
 $19,312/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -8112,7 +8112,7 @@
           <t>D | 272呎 (1房)
 $533万
 $19,599/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -8120,7 +8120,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,172/呎
-(25年-08月)</t>
+(25年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
           <t>B | 292呎 (1房)
 $576万
 $19,733/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -8151,7 +8151,7 @@
           <t>C | 205呎 (开放式)
 $399万
 $19,454/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -8159,7 +8159,7 @@
           <t>D | 272呎 (1房)
 $539万
 $19,824/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -8167,7 +8167,7 @@
           <t>E | 274呎 (1房)
 $529万
 $19,314/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
           <t>A | 316呎 (1房)
 $626万
 $19,804/呎
-(25年-07月)</t>
+(25年-07月-01日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -8190,7 +8190,7 @@
           <t>B | 292呎 (1房)
 $599万
 $20,527/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -8198,7 +8198,7 @@
           <t>C | 205呎 (开放式)
 $387万
 $18,893/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -8206,7 +8206,7 @@
           <t>D | 272呎 (1房)
 $526万
 $19,338/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -8214,7 +8214,7 @@
           <t>E | 274呎 (1房)
 $516万
 $18,832/呎
-(25年-07月)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8237,7 @@
           <t>B | 292呎 (1房)
 $571万
 $19,568/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -8245,7 +8245,7 @@
           <t>C | 205呎 (开放式)
 $394万
 $19,210/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -8253,7 +8253,7 @@
           <t>D | 272呎 (1房)
 $535万
 $19,654/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -8261,7 +8261,7 @@
           <t>E | 274呎 (1房)
 $525万
 $19,146/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -8276,7 +8276,7 @@
           <t>A | 316呎 (1房)
 $616万
 $19,484/呎
-(25年-08月)</t>
+(25年-08月-03日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -8284,7 +8284,7 @@
           <t>B | 292呎 (1房)
 $592万
 $20,277/呎
-(25年-08月)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -8292,7 +8292,7 @@
           <t>C | 205呎 (开放式)
 $379万
 $18,502/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -8300,7 +8300,7 @@
           <t>D | 272呎 (1房)
 $517万
 $19,022/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -8308,7 +8308,7 @@
           <t>E | 274呎 (1房)
 $508万
 $18,522/呎
-(25年-07月)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
           <t>A | 316呎 (1房)
 $617万
 $19,519/呎
-(25年-08月)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -8331,7 +8331,7 @@
           <t>B | 292呎 (1房)
 $561万
 $19,199/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -8339,7 +8339,7 @@
           <t>C | 205呎 (开放式)
 $383万
 $18,673/呎
-(24年-08月)</t>
+(24年-08月-22日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -8347,7 +8347,7 @@
           <t>D | 272呎 (1房)
 $509万
 $18,721/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -8355,7 +8355,7 @@
           <t>E | 274呎 (1房)
 $499万
 $18,223/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
           <t>B | 292呎 (1房)
 $554万
 $18,979/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -8386,7 +8386,7 @@
           <t>C | 205呎 (开放式)
 $369万
 $17,990/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -8394,7 +8394,7 @@
           <t>D | 235呎 (1房)
 $630万
 $26,809/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -8402,7 +8402,7 @@
           <t>E | 237呎 (1房)
 $530万
 $22,363/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -657,7 +657,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -852,14 +852,14 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>7343700</v>
+        <v>4865201</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>26999</v>
+        <v>17887</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K9" s="5" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K11" s="5" t="n">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K12" s="5" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K13" s="5" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K14" s="5" t="n">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K15" s="5" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K18" s="5" t="n">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1806,14 +1806,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>7147000</v>
+        <v>4743464</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>26276</v>
+        <v>17439</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K20" s="5" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -1930,14 +1930,14 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>7734000</v>
+        <v>5133056</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>26486</v>
+        <v>17579</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K22" s="5" t="n">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2054,14 +2054,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>5979000</v>
+        <v>4544040</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>21821</v>
+        <v>16584</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>5979000</v>
+        <v>4364670</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>21982</v>
+        <v>16047</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2240,14 +2240,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>6979000</v>
+        <v>5443620</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>23901</v>
+        <v>18643</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K27" s="5" t="n">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>24.75%</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>5807000</v>
+        <v>4369768</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>21193</v>
+        <v>15948</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2426,14 +2426,14 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>26.75%</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>5900000</v>
+        <v>4321750</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>21691</v>
+        <v>15889</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.75%</t>
         </is>
       </c>
       <c r="K30" s="5" t="n">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -2550,14 +2550,14 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>6578000</v>
+        <v>5097950</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>22527</v>
+        <v>17459</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28.25%</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>5631000</v>
+        <v>4040242</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>20551</v>
+        <v>14745</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2736,14 +2736,14 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.25%</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>5539000</v>
+        <v>3752672</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>20364</v>
+        <v>13797</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2798,14 +2798,14 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>4840000</v>
+        <v>3775200</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>23495</v>
+        <v>18326</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25.25%</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>6501000</v>
+        <v>4859498</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>22264</v>
+        <v>16642</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.63%</t>
         </is>
       </c>
       <c r="K37" s="5" t="n">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -2984,14 +2984,14 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28.75%</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>5759000</v>
+        <v>4103288</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>21018</v>
+        <v>14976</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29.75%</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>5670000</v>
+        <v>3983175</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>20846</v>
+        <v>14644</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>4790000</v>
+        <v>3736200</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>23252</v>
+        <v>18137</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3170,14 +3170,14 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>6137000</v>
+        <v>4265215</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>21017</v>
+        <v>14607</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3294,14 +3294,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>5519000</v>
+        <v>3918490</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>20142</v>
+        <v>14301</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3356,14 +3356,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>5430000</v>
+        <v>3692400</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>19963</v>
+        <v>13575</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3418,14 +3418,14 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>4341000</v>
+        <v>3125520</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>21073</v>
+        <v>15172</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>6076000</v>
+        <v>4207630</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>20808</v>
+        <v>14410</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.75%</t>
         </is>
       </c>
       <c r="K47" s="5" t="n">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3604,14 +3604,14 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>5473000</v>
+        <v>3749005</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>19974</v>
+        <v>13682</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3666,14 +3666,14 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>5385000</v>
+        <v>3634875</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>19798</v>
+        <v>13364</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3728,14 +3728,14 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>4375000</v>
+        <v>3171875</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>21238</v>
+        <v>15397</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28.25%</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>6324000</v>
+        <v>4537470</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>21658</v>
+        <v>15539</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>6461000</v>
+        <v>4361175</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>20446</v>
+        <v>13801</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -3914,14 +3914,14 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>5419000</v>
+        <v>3739110</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>19777</v>
+        <v>13646</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -3976,14 +3976,14 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.25%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>5321000</v>
+        <v>3604978</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>19562</v>
+        <v>13254</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4038,14 +4038,14 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>4251000</v>
+        <v>3039465</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>20636</v>
+        <v>14755</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>5983000</v>
+        <v>4158185</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>20490</v>
+        <v>14240</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>6391000</v>
+        <v>4409790</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>20225</v>
+        <v>13955</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4224,14 +4224,14 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.25%</t>
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>5364000</v>
+        <v>3687750</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>19577</v>
+        <v>13459</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4286,14 +4286,14 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.25%</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>5288000</v>
+        <v>3582620</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>19441</v>
+        <v>13171</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28.75%</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>4208000</v>
+        <v>2998200</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>20427</v>
+        <v>14554</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4410,14 +4410,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>5925000</v>
+        <v>4103062</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>20291</v>
+        <v>14052</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4472,14 +4472,14 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>6354000</v>
+        <v>4320720</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>20108</v>
+        <v>13673</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4534,14 +4534,14 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.25%</t>
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>5332000</v>
+        <v>3665750</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>19460</v>
+        <v>13379</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>5411000</v>
+        <v>3760645</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>19893</v>
+        <v>13826</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K65" s="5" t="n">
-        <v>4034000</v>
+        <v>2783460</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>19583</v>
+        <v>13512</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4720,14 +4720,14 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
-        <v>6185000</v>
+        <v>4515050</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>21182</v>
+        <v>15462</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4782,14 +4782,14 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.25%</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>6435000</v>
+        <v>4488412</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>20364</v>
+        <v>14204</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4844,14 +4844,14 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>5368000</v>
+        <v>3730760</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>19591</v>
+        <v>13616</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>5468000</v>
+        <v>3854940</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>20103</v>
+        <v>14173</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -4968,14 +4968,14 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.25%</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>4062000</v>
+        <v>2833245</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>19815</v>
+        <v>13821</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.25%</t>
         </is>
       </c>
       <c r="K71" s="5" t="n">
-        <v>5844000</v>
+        <v>4076190</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>20014</v>
+        <v>13960</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>6271000</v>
+        <v>4295635</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>19845</v>
+        <v>13594</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5154,14 +5154,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>5253000</v>
+        <v>3598305</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>19172</v>
+        <v>13132</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5216,14 +5216,14 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>5331000</v>
+        <v>3691718</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>19599</v>
+        <v>13572</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K75" s="5" t="n">
-        <v>3959000</v>
+        <v>2711915</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>19312</v>
+        <v>13229</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5340,14 +5340,14 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.25%</t>
         </is>
       </c>
       <c r="K76" s="5" t="n">
-        <v>5814000</v>
+        <v>4055265</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>19911</v>
+        <v>13888</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5402,14 +5402,14 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>6342000</v>
+        <v>4407690</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>20070</v>
+        <v>13948</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5464,14 +5464,14 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>5292000</v>
+        <v>3664710</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>19314</v>
+        <v>13375</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5526,14 +5526,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>29.75%</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>5392000</v>
+        <v>3787880</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>19824</v>
+        <v>13926</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5588,14 +5588,14 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>3988000</v>
+        <v>2761690</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>19454</v>
+        <v>13472</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5650,14 +5650,14 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>5762000</v>
+        <v>4004590</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>19733</v>
+        <v>13714</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -5774,14 +5774,14 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>5160000</v>
+        <v>3508800</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>18832</v>
+        <v>12806</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5836,14 +5836,14 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>5260000</v>
+        <v>3629400</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>19338</v>
+        <v>13343</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.25%</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>3873000</v>
+        <v>2623958</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>18893</v>
+        <v>12800</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>27.75%</t>
         </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>5994000</v>
+        <v>4330665</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>20527</v>
+        <v>14831</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>6258000</v>
+        <v>4333665</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>19804</v>
+        <v>13714</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>5246000</v>
+        <v>3619740</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>19146</v>
+        <v>13211</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6146,14 +6146,14 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>5346000</v>
+        <v>3742200</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>19654</v>
+        <v>13758</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.25%</t>
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>3938000</v>
+        <v>2707375</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>19210</v>
+        <v>13207</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6270,14 +6270,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>5714000</v>
+        <v>3956945</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>19568</v>
+        <v>13551</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K92" s="5" t="n">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>120 天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -6394,14 +6394,14 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>5075000</v>
+        <v>3425625</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>18522</v>
+        <v>12502</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6456,14 +6456,14 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>5174000</v>
+        <v>3544190</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>19022</v>
+        <v>13030</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6518,14 +6518,14 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>3793000</v>
+        <v>2541310</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>18502</v>
+        <v>12397</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6580,14 +6580,14 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>5921000</v>
+        <v>4263120</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>20277</v>
+        <v>14600</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6642,14 +6642,14 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.25%</t>
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>6157000</v>
+        <v>4232938</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>19484</v>
+        <v>13395</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="K98" s="5" t="n">
-        <v>4993000</v>
+        <v>3345310</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>18223</v>
+        <v>12209</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>5092000</v>
+        <v>3462560</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>18721</v>
+        <v>12730</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6828,14 +6828,14 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="K100" s="5" t="n">
-        <v>3828000</v>
+        <v>2603040</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>18673</v>
+        <v>12698</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -6890,14 +6890,14 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="K101" s="5" t="n">
-        <v>5606000</v>
+        <v>3868140</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>19199</v>
+        <v>13247</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -6952,14 +6952,14 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30.75%</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
-        <v>6168000</v>
+        <v>4271340</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>19519</v>
+        <v>13517</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>5300000</v>
+        <v>3511250</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>22363</v>
+        <v>14815</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7076,14 +7076,14 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K104" s="5" t="n">
-        <v>6300000</v>
+        <v>4173750</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>26809</v>
+        <v>17761</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7138,14 +7138,14 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>3688000</v>
+        <v>2443300</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>17990</v>
+        <v>11919</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>5542000</v>
+        <v>3796270</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>18979</v>
+        <v>13001</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>33.75%</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">

--- a/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-弦岸.xlsx
@@ -657,7 +657,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -852,14 +852,14 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>4865201</v>
+        <v>7343700</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>17887</v>
+        <v>26999</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1806,14 +1806,14 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>4743464</v>
+        <v>7147000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>17439</v>
+        <v>26276</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -1930,14 +1930,14 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>33.63%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>5133056</v>
+        <v>7734000</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>17579</v>
+        <v>26486</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -2054,14 +2054,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>4544040</v>
+        <v>5979000</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>16584</v>
+        <v>21821</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>4364670</v>
+        <v>5979000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>16047</v>
+        <v>21982</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2240,14 +2240,14 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5443620</v>
+        <v>6979000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>18643</v>
+        <v>23901</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>24.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>4369768</v>
+        <v>5807000</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>15948</v>
+        <v>21193</v>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
@@ -2426,14 +2426,14 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>26.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>4321750</v>
+        <v>5900000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>15889</v>
+        <v>21691</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -2550,14 +2550,14 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>5097950</v>
+        <v>6578000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>17459</v>
+        <v>22527</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -2674,14 +2674,14 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>28.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>4040242</v>
+        <v>5631000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>14745</v>
+        <v>20551</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2736,14 +2736,14 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>32.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>3752672</v>
+        <v>5539000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>13797</v>
+        <v>20364</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2798,14 +2798,14 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>3775200</v>
+        <v>4840000</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>18326</v>
+        <v>23495</v>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>25.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>4859498</v>
+        <v>6501000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>16642</v>
+        <v>22264</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -2984,14 +2984,14 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>28.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>4103288</v>
+        <v>5759000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>14976</v>
+        <v>21018</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>29.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>3983175</v>
+        <v>5670000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>14644</v>
+        <v>20846</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3108,14 +3108,14 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>3736200</v>
+        <v>4790000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>18137</v>
+        <v>23252</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3170,14 +3170,14 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>4265215</v>
+        <v>6137000</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>14607</v>
+        <v>21017</v>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -3294,14 +3294,14 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>3918490</v>
+        <v>5519000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>14301</v>
+        <v>20142</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3356,14 +3356,14 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>3692400</v>
+        <v>5430000</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>13575</v>
+        <v>19963</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -3418,14 +3418,14 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>3125520</v>
+        <v>4341000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>15172</v>
+        <v>21073</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3480,14 +3480,14 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>4207630</v>
+        <v>6076000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>14410</v>
+        <v>20808</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -3604,14 +3604,14 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>3749005</v>
+        <v>5473000</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>13682</v>
+        <v>19974</v>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
@@ -3666,14 +3666,14 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>3634875</v>
+        <v>5385000</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>13364</v>
+        <v>19798</v>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
@@ -3728,14 +3728,14 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>3171875</v>
+        <v>4375000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>15397</v>
+        <v>21238</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -3790,14 +3790,14 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>28.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>4537470</v>
+        <v>6324000</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>15539</v>
+        <v>21658</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>4361175</v>
+        <v>6461000</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>13801</v>
+        <v>20446</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
@@ -3914,14 +3914,14 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>3739110</v>
+        <v>5419000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>13646</v>
+        <v>19777</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -3976,14 +3976,14 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>32.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>3604978</v>
+        <v>5321000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>13254</v>
+        <v>19562</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4038,14 +4038,14 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>3039465</v>
+        <v>4251000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>14755</v>
+        <v>20636</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4100,14 +4100,14 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>4158185</v>
+        <v>5983000</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>14240</v>
+        <v>20490</v>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
@@ -4162,14 +4162,14 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>4409790</v>
+        <v>6391000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>13955</v>
+        <v>20225</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4224,14 +4224,14 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>31.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>3687750</v>
+        <v>5364000</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>13459</v>
+        <v>19577</v>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
@@ -4286,14 +4286,14 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>32.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>3582620</v>
+        <v>5288000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>13171</v>
+        <v>19441</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4348,14 +4348,14 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>28.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>2998200</v>
+        <v>4208000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>14554</v>
+        <v>20427</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4410,14 +4410,14 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>4103062</v>
+        <v>5925000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>14052</v>
+        <v>20291</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4472,14 +4472,14 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>4320720</v>
+        <v>6354000</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>13673</v>
+        <v>20108</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4534,14 +4534,14 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>31.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="5" t="n">
-        <v>3665750</v>
+        <v>5332000</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>13379</v>
+        <v>19460</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4596,14 +4596,14 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="5" t="n">
-        <v>3760645</v>
+        <v>5411000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>13826</v>
+        <v>19893</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="5" t="n">
-        <v>2783460</v>
+        <v>4034000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>13512</v>
+        <v>19583</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4720,14 +4720,14 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="5" t="n">
-        <v>4515050</v>
+        <v>6185000</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>15462</v>
+        <v>21182</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4782,14 +4782,14 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>30.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="5" t="n">
-        <v>4488412</v>
+        <v>6435000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>14204</v>
+        <v>20364</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4844,14 +4844,14 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="5" t="n">
-        <v>3730760</v>
+        <v>5368000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>13616</v>
+        <v>19591</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4906,14 +4906,14 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>3854940</v>
+        <v>5468000</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>14173</v>
+        <v>20103</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -4968,14 +4968,14 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>30.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="5" t="n">
-        <v>2833245</v>
+        <v>4062000</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>13821</v>
+        <v>19815</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5030,14 +5030,14 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>30.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="5" t="n">
-        <v>4076190</v>
+        <v>5844000</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>13960</v>
+        <v>20014</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5092,14 +5092,14 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="5" t="n">
-        <v>4295635</v>
+        <v>6271000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>13594</v>
+        <v>19845</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5154,14 +5154,14 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="5" t="n">
-        <v>3598305</v>
+        <v>5253000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>13132</v>
+        <v>19172</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5216,14 +5216,14 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="5" t="n">
-        <v>3691718</v>
+        <v>5331000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>13572</v>
+        <v>19599</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5278,14 +5278,14 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="5" t="n">
-        <v>2711915</v>
+        <v>3959000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>13229</v>
+        <v>19312</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5340,14 +5340,14 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>30.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="5" t="n">
-        <v>4055265</v>
+        <v>5814000</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>13888</v>
+        <v>19911</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5402,14 +5402,14 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K77" s="5" t="n">
-        <v>4407690</v>
+        <v>6342000</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>13948</v>
+        <v>20070</v>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
@@ -5464,14 +5464,14 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>3664710</v>
+        <v>5292000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>13375</v>
+        <v>19314</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5526,14 +5526,14 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>29.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="5" t="n">
-        <v>3787880</v>
+        <v>5392000</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>13926</v>
+        <v>19824</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5588,14 +5588,14 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>2761690</v>
+        <v>3988000</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>13472</v>
+        <v>19454</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5650,14 +5650,14 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="5" t="n">
-        <v>4004590</v>
+        <v>5762000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>13714</v>
+        <v>19733</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N82" s="3" t="inlineStr">
@@ -5774,14 +5774,14 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K83" s="5" t="n">
-        <v>3508800</v>
+        <v>5160000</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>12806</v>
+        <v>18832</v>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
@@ -5836,14 +5836,14 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="5" t="n">
-        <v>3629400</v>
+        <v>5260000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>13343</v>
+        <v>19338</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -5898,14 +5898,14 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>32.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="5" t="n">
-        <v>2623958</v>
+        <v>3873000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>12800</v>
+        <v>18893</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>27.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>4330665</v>
+        <v>5994000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>14831</v>
+        <v>20527</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6022,14 +6022,14 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>4333665</v>
+        <v>6258000</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>13714</v>
+        <v>19804</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6084,14 +6084,14 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>3619740</v>
+        <v>5246000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>13211</v>
+        <v>19146</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6146,14 +6146,14 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="5" t="n">
-        <v>3742200</v>
+        <v>5346000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>13758</v>
+        <v>19654</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>31.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="5" t="n">
-        <v>2707375</v>
+        <v>3938000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>13207</v>
+        <v>19210</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6270,14 +6270,14 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>3956945</v>
+        <v>5714000</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>13551</v>
+        <v>19568</v>
       </c>
       <c r="M91" s="3" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金付款計劃</t>
         </is>
       </c>
       <c r="N92" s="3" t="inlineStr">
@@ -6394,14 +6394,14 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>3425625</v>
+        <v>5075000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>12502</v>
+        <v>18522</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -6456,14 +6456,14 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>3544190</v>
+        <v>5174000</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>13030</v>
+        <v>19022</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6518,14 +6518,14 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>2541310</v>
+        <v>3793000</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>12397</v>
+        <v>18502</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6580,14 +6580,14 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>4263120</v>
+        <v>5921000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>14600</v>
+        <v>20277</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6642,14 +6642,14 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>31.25%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K97" s="5" t="n">
-        <v>4232938</v>
+        <v>6157000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>13395</v>
+        <v>19484</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6704,14 +6704,14 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="5" t="n">
-        <v>3345310</v>
+        <v>4993000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>12209</v>
+        <v>18223</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="5" t="n">
-        <v>3462560</v>
+        <v>5092000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>12730</v>
+        <v>18721</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -6828,14 +6828,14 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="5" t="n">
-        <v>2603040</v>
+        <v>3828000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>12698</v>
+        <v>18673</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -6890,14 +6890,14 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K101" s="5" t="n">
-        <v>3868140</v>
+        <v>5606000</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>13247</v>
+        <v>19199</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -6952,14 +6952,14 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>30.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="5" t="n">
-        <v>4271340</v>
+        <v>6168000</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>13517</v>
+        <v>19519</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -7014,14 +7014,14 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K103" s="5" t="n">
-        <v>3511250</v>
+        <v>5300000</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>14815</v>
+        <v>22363</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7076,14 +7076,14 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="5" t="n">
-        <v>4173750</v>
+        <v>6300000</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>17761</v>
+        <v>26809</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7138,14 +7138,14 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K105" s="5" t="n">
-        <v>2443300</v>
+        <v>3688000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>11919</v>
+        <v>17990</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7200,14 +7200,14 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="5" t="n">
-        <v>3796270</v>
+        <v>5542000</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>13001</v>
+        <v>18979</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>33.75%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="L107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M107" s="3" t="inlineStr">
